--- a/HLJT_online_OpenSesame/Messages.xlsx
+++ b/HLJT_online_OpenSesame/Messages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/HLJT/HLJT_online_OpenSesame/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A75F091B-10EB-4654-8202-B55275050D1E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="114_{76620BA0-2F4E-4B7F-9814-47832B9E28A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33405" yWindow="120" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>EN</t>
   </si>
@@ -252,16 +252,6 @@
     <t>DE</t>
   </si>
   <si>
-    <t>Willkommen zur Hand-Lateralitäts-Bewertungsaufgabe!
-Zweck der Aufgabe ist es, Ihre Fähigkeit zu messen, Lateralisierungen (rechts/links) von Handbildern zu beurteilen.
-Drücken Sie die LEERTASTE, um zu starten.</t>
-  </si>
-  <si>
-    <t>Dies ist das Ende des Experiments.
-Vielen Dank für Ihre Teilnahme!
-Warten Sie 3 Sekunden, bevor Sie das Experiment beenden.</t>
-  </si>
-  <si>
     <t>Drücken Sie die LEERTASTE, um fortzufahren</t>
   </si>
   <si>
@@ -281,11 +271,6 @@
 Eine Meldung unten wird Ihnen anzeigen, wann Sie weitermachen können.</t>
   </si>
   <si>
-    <t>Sie werden nun mit einem Hauptaufgabenblock beginnen.
-Ihre Leistung ist in diesem Block wichtig.
-Sie müssen so SCHNELL UND GENAU wie möglich antworten.</t>
-  </si>
-  <si>
     <t>Sie haben den Block abgeschlossen.
 Nehmen Sie sich ein paar Sekunden Zeit, bevor Sie fortfahren.
 Eine Meldung unten wird Ihnen anzeigen, wann Sie weitermachen können.</t>
@@ -357,9 +342,6 @@
     <t>Beidhändig</t>
   </si>
   <si>
-    <t>Rechte</t>
-  </si>
-  <si>
     <t>Ambidextre</t>
   </si>
   <si>
@@ -384,6 +366,9 @@
     <t>pns_msg</t>
   </si>
   <si>
+    <t>Prefer not saying</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
@@ -414,6 +399,9 @@
     <t>Otro</t>
   </si>
   <si>
+    <t>Prefiero no decirlo</t>
+  </si>
+  <si>
     <t>Femme</t>
   </si>
   <si>
@@ -429,6 +417,9 @@
     <t>Autre</t>
   </si>
   <si>
+    <t>Préfère ne pas le dire</t>
+  </si>
+  <si>
     <t>Weiblich</t>
   </si>
   <si>
@@ -444,6 +435,9 @@
     <t>Sonstiges</t>
   </si>
   <si>
+    <t>Möchte ich nicht sagen</t>
+  </si>
+  <si>
     <t>next_msg</t>
   </si>
   <si>
@@ -487,22 +481,6 @@
   </si>
   <si>
     <t>Dominance manuelle :</t>
-  </si>
-  <si>
-    <t>Prefer not
-saying</t>
-  </si>
-  <si>
-    <t>Prefiero no
-decirlo</t>
-  </si>
-  <si>
-    <t>Préfère ne
-pas le dire</t>
-  </si>
-  <si>
-    <t>Möchte ich
-nicht sagen</t>
   </si>
   <si>
     <t>Has terminado el bloque de práctica.
@@ -510,26 +488,93 @@
 Verás un mensaje más abajo indicando que ya puedes seguir.</t>
   </si>
   <si>
-    <t>age_question_msg</t>
-  </si>
-  <si>
-    <t>Please type in your age and hit ENTER</t>
-  </si>
-  <si>
-    <t>Escribe tu edad y pressiona ENTER</t>
-  </si>
-  <si>
-    <t>Indique ton âge et appuyez sur ENTER</t>
-  </si>
-  <si>
-    <t>Gib dein Alter ein und drücke die ENTER-Taste</t>
+    <r>
+      <t xml:space="preserve">Willkommen zur Hand-Lateralitäts-Bewertungsaufgabe!
+Zweck der Aufgabe ist es, Ihre Fähigkeit zu messen, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lateralität</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (rechts/links) von Handbildern zu beurteilen.
+Drücken Sie die LEERTASTE, um zu starten.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dies ist das Ende des Experiments.
+Vielen Dank für Ihre Teilnahme!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Das Experiment endet in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3 Sekunden</t>
+    </r>
+  </si>
+  <si>
+    <t>Sie werden nun mit einem Hauptaufgabenblock beginnen.
+Ihre Leistung ist in diesem Block wichtig.
+Sie müssen so SCHNELL UND KORREKT wie möglich antworten.</t>
+  </si>
+  <si>
+    <t>Rechts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,6 +604,13 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -623,10 +675,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -926,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.7265625" style="1"/>
@@ -963,7 +1011,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -980,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -997,7 +1045,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1014,7 +1062,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1031,7 +1079,7 @@
         <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1048,7 +1096,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1059,13 +1107,13 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1082,7 +1130,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1099,89 +1147,89 @@
         <v>34</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
-        <v>124</v>
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>95</v>
@@ -1189,16 +1237,16 @@
     </row>
     <row r="16" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>96</v>
@@ -1206,16 +1254,16 @@
     </row>
     <row r="17" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>97</v>
@@ -1223,16 +1271,16 @@
     </row>
     <row r="18" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="C18" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>98</v>
@@ -1240,16 +1288,16 @@
     </row>
     <row r="19" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>99</v>
@@ -1257,103 +1305,86 @@
     </row>
     <row r="20" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C22" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E24" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1370,21 +1401,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -1498,17 +1514,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1522,17 +1554,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>